--- a/AAII_Financials/Quarterly/GOOGL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GOOGL_QTR_FIN.xlsx
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>119796000</v>
+      </c>
+      <c r="E8" s="3">
         <v>109896000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>113829000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>102346000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>96428000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>90234000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>96469000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>88268000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>84742000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>80539000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>86310000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>76693000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>74604000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>69787000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>76048000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>69092000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>69685000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>68011000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>75325000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>65118000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>61880000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>55314000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>56898000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>46173000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>38297000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>41159000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>46075000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>40499000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>38944000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>36339000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>39276000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>33740000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>32657000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>31146000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>32323000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>27772000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>26010000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>24750000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>26064000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>22451000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>45943000</v>
+      </c>
+      <c r="E9" s="3">
         <v>41271000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>45767000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>41369000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>39039000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>36361000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>40613000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>36474000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>35507000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>33712000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>37575000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>33229000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>31916000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>30612000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>35342000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>31158000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>30104000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>29599000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>32988000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>27621000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>26227000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>24103000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>26080000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>21117000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>18553000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>18982000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>21020000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>17568000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>17296000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>16012000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>17918000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>14281000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>13883000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>13467000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>14267000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>11148000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>10373000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>9795000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>10661000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>8699000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>73853000</v>
+      </c>
+      <c r="E10" s="3">
         <v>68625000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>68062000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>60977000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>57389000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>53873000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>55856000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>51794000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>49235000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>46827000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>48735000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>43464000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>42688000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>39175000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>40706000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>37934000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>39581000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>38412000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>42337000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>37497000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>35653000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>31211000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>30818000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>25056000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>19744000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>22177000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>25055000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>22931000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>21648000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>20327000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>21358000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>19459000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>18774000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>17679000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>18056000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>16624000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>15637000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>14955000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>15403000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>13752000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,130 +1219,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>18219000</v>
+      </c>
+      <c r="E12" s="3">
         <v>17032000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>18572000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>15151000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>13808000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>13556000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>13116000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12447000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>11860000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>11903000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12113000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>11258000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>10588000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>11468000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>10267000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>10273000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>9841000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>9119000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>8708000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7694000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>7675000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7485000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7022000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>6856000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>6875000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>6820000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7222000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>6554000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>6213000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>6029000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>6034000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>5232000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>5114000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>5039000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>4306000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>4205000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>4172000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>3942000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>3622000</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>3596000</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1451,52 +1467,55 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-98999000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-36804000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-2353000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-10856000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1451000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-9960000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>67000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1981000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1024000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-1781000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-471000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>869000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>509000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-84000</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>10</v>
@@ -1507,14 +1526,14 @@
       <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1541,31 +1560,31 @@
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>1697000</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>5071000</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
         <v>0</v>
       </c>
       <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>2736000</v>
-      </c>
-      <c r="AN14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AO14" s="3" t="s">
         <v>10</v>
@@ -1573,53 +1592,56 @@
       <c r="AP14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7471000</v>
+      </c>
+      <c r="E15" s="3">
         <v>6660000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>6040000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5611000</v>
       </c>
-      <c r="G15" s="3">
-        <v>4998000</v>
-      </c>
       <c r="H15" s="3">
+        <v>5122000</v>
+      </c>
+      <c r="I15" s="3">
         <v>4609000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4205000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3985000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3708000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3413000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3316000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3171000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2824000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2635000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>79026000</v>
+      </c>
+      <c r="E17" s="3">
         <v>70200000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>77895000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>71118000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>65157000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>59628000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>65497000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>59747000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>57317000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>55067000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>62613000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>55350000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>52766000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>52372000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>57888000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>51957000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>50232000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>47917000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>53440000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>44087000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>42519000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>38877000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>41247000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>34960000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>31914000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>33182000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>36809000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>31322000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>29764000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>29731000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>31055000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>25115000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>29612000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>24145000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>24659000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>19990000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>21878000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>18182000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>19425000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>16684000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>40770000</v>
+      </c>
+      <c r="E18" s="3">
         <v>39696000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>35934000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>31228000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>31271000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>30606000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>30972000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>28521000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>27425000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>25472000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>23697000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>21343000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>21838000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>17415000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>18160000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>17135000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>19453000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>20094000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>21885000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>21031000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>19361000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>16437000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>15651000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11213000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>6383000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>7977000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>9266000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>9177000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>9180000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>6608000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>8221000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>8625000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3045000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>7001000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>7664000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>7782000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>4132000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>6568000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>6639000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>5767000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,618 +2056,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1168000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-64000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>81000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-970000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-422000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-256000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-303000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-15000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-127000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-95000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>797000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>227000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>275000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>11000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-923000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-801000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-356000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1077000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2634000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2110000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2700000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4922000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3091000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2194000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1907000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-199000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1455000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-526000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2992000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1573000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1880000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1486000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1197000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>3572000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>390000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>224000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>266000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>276000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>251000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>47073000</v>
+      </c>
+      <c r="E21" s="3">
         <v>46420000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>41893000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>37809000</v>
       </c>
-      <c r="G21" s="3">
-        <v>36691000</v>
-      </c>
       <c r="H21" s="3">
+        <v>36815000</v>
+      </c>
+      <c r="I21" s="3">
         <v>35471000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>35480000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>32521000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>31260000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>28980000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>26216000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>24287000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>24387000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>20039000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>21438000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>20380000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>22996000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>22799000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>27958000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>26445000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>25006000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>24112000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>22467000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>16885000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>11676000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>10886000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>14134000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>11571000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>15007000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>10794000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>12681000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>12466000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>6356000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>12559000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>10080000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>9767000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>6023000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>8347000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>8577000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>7670000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1278000</v>
+      </c>
+      <c r="E22" s="3">
         <v>533000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>298000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>143000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>261000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>34000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>53000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>54000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>67000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>94000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>69000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>116000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>43000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>80000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>90000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>101000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>83000</v>
       </c>
       <c r="T22" s="3">
         <v>83000</v>
       </c>
       <c r="U22" s="3">
+        <v>83000</v>
+      </c>
+      <c r="V22" s="3">
         <v>117000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>77000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>76000</v>
       </c>
       <c r="X22" s="3">
         <v>76000</v>
       </c>
       <c r="Y22" s="3">
+        <v>76000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>53000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>48000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>13000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>21000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>17000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>23000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>25000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>35000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>29000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>28000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>27000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>30000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>36000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>27000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>21000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>25000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>33000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>138753000</v>
+      </c>
+      <c r="E23" s="3">
         <v>77412000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>39117000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>43987000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>33933000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>41789000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>32243000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>31706000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>27551000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>28315000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>24412000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>21197000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>21903000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>18205000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>17147000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>16233000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>19014000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>18934000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>24402000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>23064000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>21985000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>21283000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>18689000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>13359000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8277000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>7757000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>10704000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8628000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>12147000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>8146000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>10072000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>10083000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>4215000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>10543000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>8018000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>7979000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>4377000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>6819000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>6857000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>6045000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>26560000</v>
+      </c>
+      <c r="E24" s="3">
         <v>14834000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4662000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9008000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5737000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7249000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5707000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5405000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3932000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4653000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3725000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1508000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3535000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3154000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3523000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2323000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3012000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2498000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3760000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4128000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3460000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3353000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3462000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2112000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1318000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>921000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>33000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1560000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2200000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1489000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1124000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>891000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1020000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1142000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1214000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1247000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>853000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1393000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>1524000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>984000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>112193000</v>
+      </c>
+      <c r="E26" s="3">
         <v>62578000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>34455000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>34979000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>28196000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>34540000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>26536000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>26301000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>23619000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>23662000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>20687000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>19689000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>18368000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>15051000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>13624000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>13910000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>16002000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>16436000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>20642000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>18936000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>18525000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>17930000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>15227000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>11247000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6959000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>6836000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>10671000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>7068000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>9947000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>6657000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>8948000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>9192000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3195000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>9401000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>6804000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>6732000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>3524000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>5426000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>5333000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>5061000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>112107000</v>
+      </c>
+      <c r="E27" s="3">
         <v>62578000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>34455000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>34979000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>28196000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>34540000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>26536000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>26301000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>23619000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>23662000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>20687000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19689000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>18368000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>15051000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>13624000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>13910000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>16002000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>16436000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>20642000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>18936000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>18525000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>17930000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>15227000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>11247000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6959000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6836000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>10671000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>7068000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>9947000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>6657000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>8948000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>9192000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>3195000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>9401000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>6804000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>6732000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>3524000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>5426000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>5333000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>5061000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3208,8 +3268,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>10</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>10</v>
@@ -3226,11 +3286,11 @@
       <c r="AJ29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-9824000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>10</v>
@@ -3238,14 +3298,17 @@
       <c r="AN29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AO29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP29" s="3" t="s">
+      <c r="AO29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,252 +3554,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1168000</v>
+      </c>
+      <c r="E32" s="3">
         <v>64000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-81000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>970000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>422000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>256000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>303000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>15000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>127000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>95000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-797000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-227000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-275000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>923000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>801000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>356000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1077000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2634000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2110000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2700000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4922000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3091000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2194000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1907000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>199000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1455000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>526000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2992000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1573000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1880000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1486000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1197000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-3572000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-390000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-224000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-266000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-276000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-251000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-307000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>112193000</v>
+      </c>
+      <c r="E33" s="3">
         <v>62578000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>34455000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>34979000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>28196000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>34540000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>26536000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>26301000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>23619000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>23662000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>20687000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19689000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>18368000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>15051000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>13624000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>13910000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>16002000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>16436000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>20642000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>18936000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>18525000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>17930000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>15227000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>11247000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6959000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6836000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>10671000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>7068000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>9947000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>6657000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>8948000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>9192000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>3195000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>9401000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-3020000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>6732000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>3524000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>5426000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>5333000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>5061000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>112193000</v>
+      </c>
+      <c r="E35" s="3">
         <v>62578000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>34455000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>34979000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>28196000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>34540000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>26536000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>26301000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>23619000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>23662000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>20687000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19689000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>18368000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>15051000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>13624000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>13910000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>16002000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>16436000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>20642000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>18936000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>18525000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>17930000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>15227000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>11247000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6959000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6836000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>10671000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>7068000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>9947000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>6657000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>8948000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>9192000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>3195000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>9401000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-3020000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>6732000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>3524000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>5426000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>5333000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>5061000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,379 +4276,389 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>55911000</v>
+      </c>
+      <c r="E41" s="3">
         <v>38063000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>30708000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>23090000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>21036000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>23264000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>23466000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>19959000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>27225000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>24493000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>24048000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>30702000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>25929000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>25924000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>21879000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>21984000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>17936000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>20886000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>20945000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>23719000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>23630000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>26622000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>26465000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>20129000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>17742000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>19644000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>18498000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>16032000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>16587000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>19148000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>16701000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>13443000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>14148000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>12658000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>10715000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>10581000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>15711000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>18132000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>12918000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>9406000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>186563000</v>
+      </c>
+      <c r="E42" s="3">
         <v>88777000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>96135000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>75406000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>74112000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>72064000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>72191000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>73271000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>73500000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>83597000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>86868000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>89233000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>92403000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>89178000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>91883000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>94275000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>107061000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>113084000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>118704000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>118284000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>112233000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>108482000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>110229000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>112467000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>103338000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>97585000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>101177000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>105145000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>104469000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>94340000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>92439000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>92973000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>88106000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>90227000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>91156000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>89562000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>79002000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>74307000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>73415000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>73650000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>69175000</v>
+      </c>
+      <c r="E43" s="3">
         <v>62999000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>62886000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>57148000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>55048000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>51000000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>52340000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>49104000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>47087000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>44552000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>47964000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>41020000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>38804000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>36036000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>40258000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>36176000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>37073000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>35622000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>40270000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>34800000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>32851000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>28499000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>31384000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>25513000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>21595000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>23735000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>27492000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>21081000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>21317000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>19260000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>21193000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>18067000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>17244000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>16814000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>18705000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>15577000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>14877000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>12969000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>14232000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>12395000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>10</v>
+      <c r="D44" s="3">
+        <v>9991000</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>10</v>
@@ -4592,705 +4687,723 @@
       <c r="M44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O44" s="3">
         <v>2957000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2231000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2315000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2670000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3156000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1980000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1369000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1170000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1278000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>907000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>888000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>728000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>835000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>815000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>889000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>999000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1401000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>964000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1053000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1107000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1212000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>698000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>636000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>749000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>765000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>398000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>280000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>268000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>559000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>21884000</v>
+      </c>
+      <c r="E45" s="3">
         <v>23914000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>16309000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>18303000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>16020000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>15724000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>15714000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15207000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14183000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>12829000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12650000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12398000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9421000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8532000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8105000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10518000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8321000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6892000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7054000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6029000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6076000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7646000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5490000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>5425000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>5579000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>5165000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>4412000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4699000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4100000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4406000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4236000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4007000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3961000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3426000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2983000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2860000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>2398000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>3106000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>4575000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>2536000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>343524000</v>
+      </c>
+      <c r="E46" s="3">
         <v>213753000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>206038000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>173947000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>166216000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>162052000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>163711000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>157541000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>161995000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>165471000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>171530000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>176310000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>168788000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>161985000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>164795000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>166109000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>172371000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>177853000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>188143000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>184110000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>175697000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>172137000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>174296000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>164369000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>149069000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>147018000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>152578000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>148358000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>147437000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>138207000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>135676000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>129702000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>124157000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>123761000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>124308000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>119345000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>112386000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>108794000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>105408000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>98546000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>131461000</v>
+      </c>
+      <c r="E47" s="3">
         <v>106946000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>68687000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>63800000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>52574000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>51029000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>37982000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>36177000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>34172000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>33994000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>31929000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>30907000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>31224000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>31213000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>30492000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>30419000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>30665000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>30544000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>29549000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>26101000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>25532000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>25294000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>20703000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>14656000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12961000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>12367000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>13078000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>12488000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>12112000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>14474000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>13859000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>12673000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>11487000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>10976000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>7813000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>7269000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>6642000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>6131000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>5878000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>5705000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>338906000</v>
+      </c>
+      <c r="E48" s="3">
         <v>296529000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>261818000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>238311000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>217486000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>198784000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>184624000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>174831000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>164761000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>156950000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>148436000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>139904000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>135677000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>132007000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>127049000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>122040000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>119621000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>117210000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>110558000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>107549000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>104675000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>100204000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>96960000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>93582000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>90315000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>87966000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>84587000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>79593000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>74604000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>69365000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>59719000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>55300000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>51672000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>48845000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>42383000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>40120000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>37676000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>35936000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>34234000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>32753000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>66933000</v>
+      </c>
+      <c r="E49" s="3">
         <v>67218000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>33380000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>33269000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>32335000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>32173000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>31885000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>31935000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>29185000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>29183000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>29198000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>30979000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>31176000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>30962000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>31044000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>31026000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>25326000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>24323000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>24373000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>24172000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>24032000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>24164000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>22620000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>22390000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>22521000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>22574000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>22603000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>19816000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>19902000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>20006000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>20108000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>20343000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>20557000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>20671000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>19439000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>19614000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>19537000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>19684000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>19775000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>19395000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>39711000</v>
+      </c>
+      <c r="E52" s="3">
         <v>17478000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>16245000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16811000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14153000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12950000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14874000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13867000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9699000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10065000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9130000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7628000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6822000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6439000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11884000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8661000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7202000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7166000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6645000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5471000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5451000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5296000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5037000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4246000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3626000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3478000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3063000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2789000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3046000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3297000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3430000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>3520000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>3737000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2682000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>3352000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>3188000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2380000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>2211000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>2202000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>3549000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>921983000</v>
+      </c>
+      <c r="E54" s="3">
         <v>703919000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>595281000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>536469000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>502053000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>475374000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>450256000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>430266000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>414770000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>407350000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>402392000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>396711000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>383044000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>369491000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>365264000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>358255000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>355185000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>357096000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>359268000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>347403000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>335387000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>327095000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>319616000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>299243000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>278492000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>273403000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>275909000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>263044000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>257101000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>245349000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>232792000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>221538000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>211610000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>206935000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>197295000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>189536000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>178621000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>172756000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>167497000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>159948000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,213 +6116,217 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>20258000</v>
+      </c>
+      <c r="E57" s="3">
         <v>16852000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12200000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10546000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8347000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8497000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7987000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7049000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6092000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6198000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7493000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5803000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5313000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4184000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5128000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6303000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4409000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3436000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6037000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4616000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4708000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4801000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5589000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4391000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4064000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4099000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5561000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4142000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3925000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3710000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4378000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3789000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3369000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3526000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3137000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2674000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>2488000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>2306000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>2041000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>2175000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5894000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3355000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5646000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8432000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7107000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6473000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6421000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5338000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3773000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3191000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4074000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4115000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2981000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2997000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>298000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>414000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>82000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>181000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>113000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>249000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>117000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1090000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1100000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1121000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1136000</v>
       </c>
-      <c r="AB58" s="3" t="s">
+      <c r="AC58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD58" s="3" t="s">
-        <v>10</v>
+      <c r="AD58" s="3">
+        <v>0</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>10</v>
@@ -6204,18 +6337,18 @@
       <c r="AG58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI58" s="3" t="s">
+      <c r="AH58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK58" s="3">
         <v>1329000</v>
       </c>
-      <c r="AK58" s="3">
-        <v>0</v>
-      </c>
       <c r="AL58" s="3">
         <v>0</v>
       </c>
@@ -6231,496 +6364,511 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>62598000</v>
+      </c>
+      <c r="E59" s="3">
         <v>55295000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>48415000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>45404000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>38218000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>42282000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>42847000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>33171000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>35058000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>36915000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>34105000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>30788000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>39030000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>33395000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>63874000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>59262000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>56863000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>58331000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>58104000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>56917000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>50916000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>49562000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>50145000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>42688000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>38458000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>36090000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>39660000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>35082000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>33075000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>31200000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>30242000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>27512000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>26534000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>20539000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>21046000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>18019000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>16197000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>12950000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>14715000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>12148000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>126111000</v>
+      </c>
+      <c r="E60" s="3">
         <v>111188000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>102745000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>99550000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>87310000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>91654000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>89122000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>80803000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>77913000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>76997000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>81814000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>86295000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>77709000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>68854000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>69300000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>65979000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>61354000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>61948000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>64254000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>61782000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>55741000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>55453000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>56834000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>48200000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>43658000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>40189000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>45221000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>39224000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>37000000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>34910000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>34620000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>31301000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>29903000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>25394000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>24183000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>20693000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>18685000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>15256000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>16756000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>14323000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>114897000</v>
+      </c>
+      <c r="E61" s="3">
         <v>92521000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>61350000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>35763000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>37561000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>24525000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>24016000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>23951000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>24946000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>25185000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>25713000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>26331000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>26451000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>26496000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14701000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>14653000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14734000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14791000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>14817000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>14288000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>14328000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>13887000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>13932000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>13902000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4018000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5016000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4554000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4082000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4074000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>4066000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>4012000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3986000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3981000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3973000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3969000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3964000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>3955000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3937000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3935000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>3938000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>17676000</v>
+      </c>
+      <c r="E62" s="3">
         <v>21464000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>15921000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>14289000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>14266000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13928000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>12034000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9672000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9456000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10917000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11486000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9471000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10518000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12095000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>25119000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>23997000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>23678000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>26353000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>28562000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>26766000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>27753000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>27742000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>26306000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>24221000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>23494000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>24539000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>24692000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>24769000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>23835000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>22901000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>16532000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>16411000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>15726000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>16743000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>16641000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>7779000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>7695000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>8614000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>7770000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>7584000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>281503000</v>
+      </c>
+      <c r="E66" s="3">
         <v>225173000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>180016000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>149602000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>139137000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>130107000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>125172000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>116147000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>114017000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>114506000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>119013000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>123509000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>115903000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>108597000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>109120000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>104629000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>99766000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>103092000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>107633000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>102836000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>97822000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>97082000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>97072000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>86323000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>71170000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>69744000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>74467000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>68075000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>64909000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>61877000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>55164000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>51698000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>49610000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>46110000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>44793000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>32436000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>30335000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>27807000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>28461000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>25845000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,13 +7659,16 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>18023000</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>493371000</v>
+      </c>
+      <c r="E72" s="3">
         <v>384024000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>324055000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>297226000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>275760000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>262628000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>245084000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>235317000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>226033000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>219770000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>211247000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>205647000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>200884000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>196625000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>195563000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>196220000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>196845000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>195221000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>191484000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>183782000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>176939000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>170580000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>163401000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>155567000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>151681000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>151068000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>152122000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>147125000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>145346000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>138720000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>134885000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>128405000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>121282000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>120008000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>113247000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>118237000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>111505000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>109420000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>105131000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>99798000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>622457000</v>
+      </c>
+      <c r="E76" s="3">
         <v>478746000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>415265000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>386867000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>362916000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>345267000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>325084000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>314119000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>300753000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>292844000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>283379000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>273202000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>267141000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>260894000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>256144000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>253626000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>255419000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>254004000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>251635000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>244567000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>237565000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>230013000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>222544000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>212920000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>207322000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>203659000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>201442000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>194969000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>192192000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>183472000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>177628000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>169840000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>162000000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>160825000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>152502000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>157100000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>148286000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>144949000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>139036000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>134103000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>112193000</v>
+      </c>
+      <c r="E81" s="3">
         <v>62578000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>34455000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>34979000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>28196000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>34540000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>26536000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>26301000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>23619000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>23662000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>20687000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19689000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>18368000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>15051000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>13624000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>13910000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>16002000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>16436000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>20642000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>18936000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>18525000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>17930000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>15227000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>11247000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6959000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6836000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>10671000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>7068000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>9947000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>6657000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>8948000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>9192000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>3195000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>9401000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-3020000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>6732000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>3524000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>5426000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>5333000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>5061000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4998000</v>
+      </c>
+      <c r="E83" s="3">
         <v>4487000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4205000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3985000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3708000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3413000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3316000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3171000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2824000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2635000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1748000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3933000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3698000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3591000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4201000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4046000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3899000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3782000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3439000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3304000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2945000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2753000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3725000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3478000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>3386000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>3108000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>3413000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>2920000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2835000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>2613000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>2580000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>2355000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>2114000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1986000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>2026000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1761000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>1625000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>1503000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>1687000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>1596000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>39069000</v>
+      </c>
+      <c r="E89" s="3">
         <v>45790000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>52402000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>48414000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>27747000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>36150000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>39113000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>30698000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>26640000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>28848000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>18915000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>30656000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>28666000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>23509000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>23614000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>23353000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>19422000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>25106000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>24934000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>25539000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>21890000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>19289000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>22677000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>17003000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>13993000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>11451000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>14427000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>15466000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>12627000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>12000000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>12987000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>13210000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>10132000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>11642000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>10268000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>9872000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>7403000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>9548000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>9413000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>9845000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-44924000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-35674000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-27851000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-23953000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-22446000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-17197000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-14276000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13061000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13186000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12012000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11019000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8055000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6888000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6289000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7595000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7276000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6828000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9786000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6383000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6819000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5496000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5942000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5479000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5406000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5391000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6005000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-6052000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-6732000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-6126000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4638000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-7081000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-5282000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-5477000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-7299000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-4307000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-3538000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-2831000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-2508000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-3078000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>1997000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-82433000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-63389000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-51776000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-27777000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-24544000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16194000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16180000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-18011000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2781000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8564000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6167000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7150000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10800000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2946000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6227000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-833000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4187000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9051000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-11016000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-10050000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-9074000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5383000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7281000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-15197000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-8448000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1847000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4703000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-8945000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-10455000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5388000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-6876000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-10408000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3374000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-7846000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-6974000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-14404000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-7172000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-2851000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-4702000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-13045000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,37 +10426,38 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2689000</v>
+      </c>
+      <c r="E96" s="3">
         <v>2542000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>2536000</v>
       </c>
       <c r="F96" s="3">
         <v>2536000</v>
       </c>
       <c r="G96" s="3">
+        <v>2536000</v>
+      </c>
+      <c r="H96" s="3">
         <v>2543000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2434000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2442000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2455000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>2466000</v>
-      </c>
-      <c r="L96" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M96" s="3" t="s">
         <v>10</v>
@@ -10238,8 +10471,8 @@
       <c r="P96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10316,8 +10549,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,370 +10924,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>61243000</v>
+      </c>
+      <c r="E100" s="3">
         <v>25077000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>7028000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-18383000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5832000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-20201000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-19036000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-20094000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-20889000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-19714000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-19308000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-18382000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-17835000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-16568000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-17629000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-18097000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-17817000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-16214000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-16511000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-15254000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-15991000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-13606000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-9270000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>546000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-7498000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-8186000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-7326000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-6954000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-4746000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-4183000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2746000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-3478000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-4937000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2018000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-3178000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-706000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-2740000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1674000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-892000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-1089000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>401000</v>
+      </c>
+      <c r="E101" s="3">
         <v>43000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-390000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>141000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-238000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-125000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-94000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-351000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-26000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>50000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>137000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-375000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-368000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>100000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>137000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-375000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-368000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>100000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-181000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-146000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>183000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-143000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>210000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>35000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>51000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-272000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>68000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-122000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>13000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>18000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-107000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-29000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-331000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>165000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>18000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>108000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>88000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>191000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-307000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>68000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>17848000</v>
+      </c>
+      <c r="E102" s="3">
         <v>7355000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7618000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2054000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2228000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-202000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3507000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7266000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2732000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>445000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6654000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4773000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>5000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4045000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-105000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4048000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2950000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-59000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2774000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>89000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2992000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>157000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>6336000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2387000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1902000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1146000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>2466000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-555000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2561000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2447000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>3258000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-705000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1490000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1943000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>134000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-5130000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-2421000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>5214000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>3512000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-4221000</v>
       </c>
     </row>
